--- a/src/nodes/LPC/compressor_blade_parameters.xlsx
+++ b/src/nodes/LPC/compressor_blade_parameters.xlsx
@@ -803,124 +803,124 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D3">
-        <v>43.078248407950049</v>
+        <v>43.325038110804336</v>
       </c>
       <c r="E3">
-        <v>42.369220466530194</v>
+        <v>42.4304828885184</v>
       </c>
       <c r="F3">
-        <v>80.946335120576222</v>
+        <v>80.865831663115571</v>
       </c>
       <c r="G3">
-        <v>80.771638929524315</v>
+        <v>80.74874271909151</v>
       </c>
       <c r="H3">
-        <v>91.467560427874034</v>
+        <v>117.60114912155233</v>
       </c>
       <c r="I3">
-        <v>143.00704677873924</v>
+        <v>95.338031185826168</v>
       </c>
       <c r="J3">
-        <v>126.35261718834684</v>
+        <v>162.45336495644591</v>
       </c>
       <c r="K3">
-        <v>109.75026529449278</v>
+        <v>73.166843529661847</v>
       </c>
       <c r="L3">
-        <v>1746.0686011935604</v>
+        <v>2244.9453443917196</v>
       </c>
       <c r="M3">
-        <v>5214.1702647945895</v>
+        <v>3476.1135098630593</v>
       </c>
       <c r="N3">
-        <v>19.08948476405914</v>
+        <v>19.089484764059137</v>
       </c>
       <c r="O3">
-        <v>36.460932396303264</v>
+        <v>36.460932396303257</v>
       </c>
       <c r="P3">
         <v>1.3813926663976253</v>
       </c>
       <c r="Q3">
-        <v>0.76744655432468711</v>
+        <v>0.767446554324687</v>
       </c>
       <c r="R3">
-        <v>240.54615015429252</v>
+        <v>350.15264151286203</v>
       </c>
       <c r="S3">
-        <v>143.6549271413387</v>
+        <v>76.867797522474476</v>
       </c>
       <c r="T3">
-        <v>42644.825159053224</v>
+        <v>54829.0609187827</v>
       </c>
       <c r="U3">
-        <v>243224.91593453163</v>
+        <v>162149.94395635443</v>
       </c>
       <c r="V3">
-        <v>2507.9838382333874</v>
+        <v>3224.5506491572105</v>
       </c>
       <c r="W3">
-        <v>4161.249136627941</v>
+        <v>2774.1660910852943</v>
       </c>
       <c r="X3">
-        <v>66.003571390163685</v>
+        <v>125.74075453041073</v>
       </c>
       <c r="Y3">
-        <v>59.4274642048599</v>
+        <v>20.716155564821971</v>
       </c>
       <c r="Z3">
-        <v>9313.2751995666968</v>
+        <v>11974.210970871473</v>
       </c>
       <c r="AA3">
-        <v>53111.406407041417</v>
+        <v>35407.604271360949</v>
       </c>
       <c r="AB3">
-        <v>95.977477517443234</v>
+        <v>123.39961395099765</v>
       </c>
       <c r="AC3">
-        <v>159.65213324909198</v>
+        <v>106.43475549939542</v>
       </c>
       <c r="AD3">
-        <v>0.59458778435515369</v>
+        <v>0.59663861029328635</v>
       </c>
       <c r="AE3">
-        <v>0.17242114537246006</v>
+        <v>0.17232904763350362</v>
       </c>
       <c r="AF3">
-        <v>65.007527966928961</v>
+        <v>124.45570987017457</v>
       </c>
       <c r="AG3">
-        <v>58.9470189258858</v>
+        <v>20.3960297978814</v>
       </c>
       <c r="AH3">
-        <v>9314.2712429899311</v>
+        <v>11975.496015531709</v>
       </c>
       <c r="AI3">
-        <v>53111.8868523204</v>
+        <v>35407.924397127885</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>2.1629257694631435E-14</v>
       </c>
       <c r="AK3">
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>9379.27877095686</v>
+        <v>12099.951725401883</v>
       </c>
       <c r="AM3">
-        <v>53170.833871246272</v>
+        <v>35428.320426925769</v>
       </c>
       <c r="AN3">
-        <v>403.93534011285863</v>
+        <v>521.105965064599</v>
       </c>
       <c r="AO3">
-        <v>1200.845087427768</v>
+        <v>800.13649294105869</v>
       </c>
       <c r="AP3">
         <v>14.793838572448902</v>
@@ -940,124 +940,124 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>90</v>
+        <v>812</v>
       </c>
       <c r="C4">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="D4">
-        <v>55.903109665134458</v>
+        <v>56.315053338411836</v>
       </c>
       <c r="E4">
-        <v>54.162119775631176</v>
+        <v>54.11538753627412</v>
       </c>
       <c r="F4">
-        <v>86.615910871039986</v>
+        <v>86.508722318729539</v>
       </c>
       <c r="G4">
-        <v>86.299212578084322</v>
+        <v>86.296543786970844</v>
       </c>
       <c r="H4">
-        <v>147.83001946415376</v>
+        <v>190.06716788248338</v>
       </c>
       <c r="I4">
-        <v>163.2443505702883</v>
+        <v>108.82956704685887</v>
       </c>
       <c r="J4">
-        <v>511.49950073782645</v>
+        <v>657.68465755550051</v>
       </c>
       <c r="K4">
-        <v>227.15739588741394</v>
+        <v>151.43826392494265</v>
       </c>
       <c r="L4">
-        <v>3587.6049109771834</v>
+        <v>4612.6348855420911</v>
       </c>
       <c r="M4">
-        <v>6359.2557610133372</v>
+        <v>4239.5038406755584</v>
       </c>
       <c r="N4">
-        <v>24.268446449383816</v>
+        <v>24.268446449383809</v>
       </c>
       <c r="O4">
         <v>38.955441574532315</v>
       </c>
       <c r="P4">
-        <v>3.4600516362771381</v>
+        <v>3.4602749379742446</v>
       </c>
       <c r="Q4">
         <v>1.3915176549378141</v>
       </c>
       <c r="R4">
-        <v>2069.4089817665663</v>
+        <v>2767.4490926720832</v>
       </c>
       <c r="S4">
-        <v>414.06805390260536</v>
+        <v>251.43015126236506</v>
       </c>
       <c r="T4">
-        <v>111392.87534619434</v>
+        <v>143219.41115939268</v>
       </c>
       <c r="U4">
-        <v>316934.49238931114</v>
+        <v>211289.66159287409</v>
       </c>
       <c r="V4">
-        <v>12903.146579510725</v>
+        <v>16589.759887942357</v>
       </c>
       <c r="W4">
-        <v>9201.9042763675461</v>
+        <v>6134.6028509116968</v>
       </c>
       <c r="X4">
-        <v>299.59429728371066</v>
+        <v>491.67935504261163</v>
       </c>
       <c r="Y4">
-        <v>97.97452707557045</v>
+        <v>40.70113337767512</v>
       </c>
       <c r="Z4">
-        <v>24327.277682598167</v>
+        <v>31277.928449054827</v>
       </c>
       <c r="AA4">
-        <v>69206.876133648</v>
+        <v>46137.91742243198</v>
       </c>
       <c r="AB4">
-        <v>489.84833696822523</v>
+        <v>628.77499547536263</v>
       </c>
       <c r="AC4">
-        <v>352.88761265248121</v>
+        <v>235.2584084349877</v>
       </c>
       <c r="AD4">
-        <v>1.1674327507274593</v>
+        <v>1.1695525618683607</v>
       </c>
       <c r="AE4">
-        <v>0.2925566389668916</v>
+        <v>0.29240042898802476</v>
       </c>
       <c r="AF4">
-        <v>289.61198883964073</v>
+        <v>478.84267547875788</v>
       </c>
       <c r="AG4">
-        <v>96.1726402350547</v>
+        <v>39.500516904168272</v>
       </c>
       <c r="AH4">
-        <v>24337.259991042236</v>
+        <v>31290.765128618685</v>
       </c>
       <c r="AI4">
-        <v>69208.678020488514</v>
+        <v>46139.118038905479</v>
       </c>
       <c r="AJ4">
-        <v>5.6497950155091811E-14</v>
+        <v>-1.1299590031018362E-13</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>4.6886447420039893E-14</v>
       </c>
       <c r="AL4">
-        <v>24626.871979881878</v>
+        <v>31769.607804097446</v>
       </c>
       <c r="AM4">
-        <v>69304.850660723561</v>
+        <v>46178.618555809648</v>
       </c>
       <c r="AN4">
-        <v>830.04240621893234</v>
+        <v>1070.7855460308531</v>
       </c>
       <c r="AO4">
-        <v>1464.5836296447237</v>
+        <v>975.86890573556263</v>
       </c>
       <c r="AP4">
         <v>18.807394940918407</v>
@@ -1077,10 +1077,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="C5">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="D5">
         <v>65.569283423161352</v>
@@ -1089,28 +1089,28 @@
         <v>64.803988411306</v>
       </c>
       <c r="F5">
-        <v>80.2430759271277</v>
+        <v>79.570873759661467</v>
       </c>
       <c r="G5">
-        <v>75.858754664869792</v>
+        <v>76.003270500804447</v>
       </c>
       <c r="H5">
         <v>90.690433622953591</v>
       </c>
       <c r="I5">
-        <v>410.0602845013932</v>
+        <v>328.04822760111449</v>
       </c>
       <c r="J5">
         <v>310.5686613571844</v>
       </c>
       <c r="K5">
-        <v>2614.5067433052936</v>
+        <v>2091.6053946442344</v>
       </c>
       <c r="L5">
         <v>2633.2450046307708</v>
       </c>
       <c r="M5">
-        <v>13866.959326974131</v>
+        <v>11093.567461579305</v>
       </c>
       <c r="N5">
         <v>29.035532188306806</v>
@@ -1122,79 +1122,79 @@
         <v>3.4244919662461504</v>
       </c>
       <c r="Q5">
-        <v>6.3759082313576521</v>
+        <v>6.3759082313576529</v>
       </c>
       <c r="R5">
         <v>1188.4719400420904</v>
       </c>
       <c r="S5">
-        <v>19659.987468660467</v>
+        <v>15325.404798188587</v>
       </c>
       <c r="T5">
         <v>97817.406173883064</v>
       </c>
       <c r="U5">
-        <v>599964.56867843145</v>
+        <v>479971.65494274505</v>
       </c>
       <c r="V5">
         <v>9374.6336591143281</v>
       </c>
       <c r="W5">
-        <v>91868.441300640246</v>
+        <v>73494.75304051218</v>
       </c>
       <c r="X5">
         <v>124.93205425659131</v>
       </c>
       <c r="Y5">
-        <v>2990.1324030801611</v>
+        <v>1989.5207457243391</v>
       </c>
       <c r="Z5">
         <v>21359.736082228217</v>
       </c>
       <c r="AA5">
-        <v>131027.27276407532</v>
+        <v>104821.81821126021</v>
       </c>
       <c r="AB5">
         <v>357.10729559844509</v>
       </c>
       <c r="AC5">
-        <v>3453.98118388411</v>
+        <v>2763.1849471072746</v>
       </c>
       <c r="AD5">
         <v>0.96318433789519375</v>
       </c>
       <c r="AE5">
-        <v>1.5441367809656457</v>
+        <v>1.5381031679748503</v>
       </c>
       <c r="AF5">
         <v>118.92825150172811</v>
       </c>
       <c r="AG5">
-        <v>2897.0241312558155</v>
+        <v>1915.3253199800497</v>
       </c>
       <c r="AH5">
         <v>21365.739884983082</v>
       </c>
       <c r="AI5">
-        <v>131120.38103589966</v>
+        <v>104896.01363700451</v>
       </c>
       <c r="AJ5">
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>4.2601894840164506E-13</v>
+        <v>0</v>
       </c>
       <c r="AL5">
         <v>21484.668136484812</v>
       </c>
       <c r="AM5">
-        <v>134017.40516715549</v>
+        <v>106811.33895698455</v>
       </c>
       <c r="AN5">
         <v>606.54941860941869</v>
       </c>
       <c r="AO5">
-        <v>3225.2286598844903</v>
+        <v>2570.4944158188341</v>
       </c>
       <c r="AP5">
         <v>22.501758500453995</v>
@@ -1678,124 +1678,124 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D3">
-        <v>43.078248407950049</v>
+        <v>43.325038110804336</v>
       </c>
       <c r="E3">
-        <v>42.369220466530194</v>
+        <v>42.4304828885184</v>
       </c>
       <c r="F3">
-        <v>80.946335120576222</v>
+        <v>80.865831663115571</v>
       </c>
       <c r="G3">
-        <v>80.771638929524315</v>
+        <v>80.74874271909151</v>
       </c>
       <c r="H3">
-        <v>91.467560427874034</v>
+        <v>117.60114912155233</v>
       </c>
       <c r="I3">
-        <v>143.00704677873924</v>
+        <v>95.338031185826168</v>
       </c>
       <c r="J3">
-        <v>126.35261718834684</v>
+        <v>162.45336495644591</v>
       </c>
       <c r="K3">
-        <v>109.75026529449278</v>
+        <v>73.166843529661847</v>
       </c>
       <c r="L3">
-        <v>1746.0686011935604</v>
+        <v>2244.9453443917196</v>
       </c>
       <c r="M3">
-        <v>5214.1702647945895</v>
+        <v>3476.1135098630593</v>
       </c>
       <c r="N3">
-        <v>19.08948476405914</v>
+        <v>19.089484764059137</v>
       </c>
       <c r="O3">
-        <v>36.460932396303264</v>
+        <v>36.460932396303257</v>
       </c>
       <c r="P3">
         <v>1.3813926663976253</v>
       </c>
       <c r="Q3">
-        <v>0.76744655432468711</v>
+        <v>0.767446554324687</v>
       </c>
       <c r="R3">
-        <v>240.54615015429252</v>
+        <v>350.15264151286203</v>
       </c>
       <c r="S3">
-        <v>143.6549271413387</v>
+        <v>76.867797522474476</v>
       </c>
       <c r="T3">
-        <v>42644.825159053224</v>
+        <v>54829.0609187827</v>
       </c>
       <c r="U3">
-        <v>243224.91593453163</v>
+        <v>162149.94395635443</v>
       </c>
       <c r="V3">
-        <v>2507.9838382333874</v>
+        <v>3224.5506491572105</v>
       </c>
       <c r="W3">
-        <v>4161.249136627941</v>
+        <v>2774.1660910852943</v>
       </c>
       <c r="X3">
-        <v>66.003571390163685</v>
+        <v>125.74075453041073</v>
       </c>
       <c r="Y3">
-        <v>59.4274642048599</v>
+        <v>20.716155564821971</v>
       </c>
       <c r="Z3">
-        <v>9313.2751995666968</v>
+        <v>11974.210970871473</v>
       </c>
       <c r="AA3">
-        <v>53111.406407041417</v>
+        <v>35407.604271360949</v>
       </c>
       <c r="AB3">
-        <v>95.977477517443234</v>
+        <v>123.39961395099765</v>
       </c>
       <c r="AC3">
-        <v>159.65213324909198</v>
+        <v>106.43475549939542</v>
       </c>
       <c r="AD3">
-        <v>0.59458778435515369</v>
+        <v>0.59663861029328635</v>
       </c>
       <c r="AE3">
-        <v>0.17242114537246006</v>
+        <v>0.17232904763350362</v>
       </c>
       <c r="AF3">
-        <v>65.007527966928961</v>
+        <v>124.45570987017457</v>
       </c>
       <c r="AG3">
-        <v>58.9470189258858</v>
+        <v>20.3960297978814</v>
       </c>
       <c r="AH3">
-        <v>9314.2712429899311</v>
+        <v>11975.496015531709</v>
       </c>
       <c r="AI3">
-        <v>53111.8868523204</v>
+        <v>35407.924397127885</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>2.1629257694631435E-14</v>
       </c>
       <c r="AK3">
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>9379.27877095686</v>
+        <v>12099.951725401883</v>
       </c>
       <c r="AM3">
-        <v>53170.833871246272</v>
+        <v>35428.320426925769</v>
       </c>
       <c r="AN3">
-        <v>403.93534011285863</v>
+        <v>521.105965064599</v>
       </c>
       <c r="AO3">
-        <v>1200.845087427768</v>
+        <v>800.13649294105869</v>
       </c>
       <c r="AP3">
         <v>14.793838572448902</v>
@@ -1815,124 +1815,124 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>90</v>
+        <v>812</v>
       </c>
       <c r="C4">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="D4">
-        <v>55.903109665134458</v>
+        <v>56.315053338411836</v>
       </c>
       <c r="E4">
-        <v>54.162119775631176</v>
+        <v>54.11538753627412</v>
       </c>
       <c r="F4">
-        <v>86.615910871039986</v>
+        <v>86.508722318729539</v>
       </c>
       <c r="G4">
-        <v>86.299212578084322</v>
+        <v>86.296543786970844</v>
       </c>
       <c r="H4">
-        <v>147.83001946415376</v>
+        <v>190.06716788248338</v>
       </c>
       <c r="I4">
-        <v>163.2443505702883</v>
+        <v>108.82956704685887</v>
       </c>
       <c r="J4">
-        <v>511.49950073782645</v>
+        <v>657.68465755550051</v>
       </c>
       <c r="K4">
-        <v>227.15739588741394</v>
+        <v>151.43826392494265</v>
       </c>
       <c r="L4">
-        <v>3587.6049109771834</v>
+        <v>4612.6348855420911</v>
       </c>
       <c r="M4">
-        <v>6359.2557610133372</v>
+        <v>4239.5038406755584</v>
       </c>
       <c r="N4">
-        <v>24.268446449383816</v>
+        <v>24.268446449383809</v>
       </c>
       <c r="O4">
         <v>38.955441574532315</v>
       </c>
       <c r="P4">
-        <v>3.4600516362771381</v>
+        <v>3.4602749379742446</v>
       </c>
       <c r="Q4">
         <v>1.3915176549378141</v>
       </c>
       <c r="R4">
-        <v>2069.4089817665663</v>
+        <v>2767.4490926720832</v>
       </c>
       <c r="S4">
-        <v>414.06805390260536</v>
+        <v>251.43015126236506</v>
       </c>
       <c r="T4">
-        <v>111392.87534619434</v>
+        <v>143219.41115939268</v>
       </c>
       <c r="U4">
-        <v>316934.49238931114</v>
+        <v>211289.66159287409</v>
       </c>
       <c r="V4">
-        <v>12903.146579510725</v>
+        <v>16589.759887942357</v>
       </c>
       <c r="W4">
-        <v>9201.9042763675461</v>
+        <v>6134.6028509116968</v>
       </c>
       <c r="X4">
-        <v>299.59429728371066</v>
+        <v>491.67935504261163</v>
       </c>
       <c r="Y4">
-        <v>97.97452707557045</v>
+        <v>40.70113337767512</v>
       </c>
       <c r="Z4">
-        <v>24327.277682598167</v>
+        <v>31277.928449054827</v>
       </c>
       <c r="AA4">
-        <v>69206.876133648</v>
+        <v>46137.91742243198</v>
       </c>
       <c r="AB4">
-        <v>489.84833696822523</v>
+        <v>628.77499547536263</v>
       </c>
       <c r="AC4">
-        <v>352.88761265248121</v>
+        <v>235.2584084349877</v>
       </c>
       <c r="AD4">
-        <v>1.1674327507274593</v>
+        <v>1.1695525618683607</v>
       </c>
       <c r="AE4">
-        <v>0.2925566389668916</v>
+        <v>0.29240042898802476</v>
       </c>
       <c r="AF4">
-        <v>289.61198883964073</v>
+        <v>478.84267547875788</v>
       </c>
       <c r="AG4">
-        <v>96.1726402350547</v>
+        <v>39.500516904168272</v>
       </c>
       <c r="AH4">
-        <v>24337.259991042236</v>
+        <v>31290.765128618685</v>
       </c>
       <c r="AI4">
-        <v>69208.678020488514</v>
+        <v>46139.118038905479</v>
       </c>
       <c r="AJ4">
-        <v>5.6497950155091811E-14</v>
+        <v>-1.1299590031018362E-13</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>4.6886447420039893E-14</v>
       </c>
       <c r="AL4">
-        <v>24626.871979881878</v>
+        <v>31769.607804097446</v>
       </c>
       <c r="AM4">
-        <v>69304.850660723561</v>
+        <v>46178.618555809648</v>
       </c>
       <c r="AN4">
-        <v>830.04240621893234</v>
+        <v>1070.7855460308531</v>
       </c>
       <c r="AO4">
-        <v>1464.5836296447237</v>
+        <v>975.86890573556263</v>
       </c>
       <c r="AP4">
         <v>18.807394940918407</v>
@@ -1952,124 +1952,124 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="C5">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="D5">
-        <v>73.266393237669</v>
+        <v>73.498067822029242</v>
       </c>
       <c r="E5">
-        <v>71.764092889790192</v>
+        <v>71.708453551402457</v>
       </c>
       <c r="F5">
-        <v>87.862053097057782</v>
+        <v>87.698169729008143</v>
       </c>
       <c r="G5">
-        <v>87.142005779924091</v>
+        <v>87.154805161518439</v>
       </c>
       <c r="H5">
-        <v>185.61849811915124</v>
+        <v>222.7421977429814</v>
       </c>
       <c r="I5">
-        <v>221.56851216319822</v>
+        <v>166.17638412239867</v>
       </c>
       <c r="J5">
-        <v>759.95135104457813</v>
+        <v>911.94162125349374</v>
       </c>
       <c r="K5">
-        <v>530.62383823729112</v>
+        <v>397.9678786779682</v>
       </c>
       <c r="L5">
-        <v>5972.505496641691</v>
+        <v>7167.0065959700287</v>
       </c>
       <c r="M5">
-        <v>8708.4676960692723</v>
+        <v>6531.3507720519528</v>
       </c>
       <c r="N5">
-        <v>32.176240822764605</v>
+        <v>32.176240822764619</v>
       </c>
       <c r="O5">
         <v>39.303724211746172</v>
       </c>
       <c r="P5">
-        <v>4.0941574182803384</v>
+        <v>4.0941574182803393</v>
       </c>
       <c r="Q5">
         <v>2.3948521974388464</v>
       </c>
       <c r="R5">
-        <v>3559.2104698668977</v>
+        <v>4346.6690183799747</v>
       </c>
       <c r="S5">
-        <v>1560.3294127598374</v>
+        <v>1116.6815464091371</v>
       </c>
       <c r="T5">
-        <v>245859.47207576979</v>
+        <v>295031.36649092374</v>
       </c>
       <c r="U5">
-        <v>437895.55001165194</v>
+        <v>328421.662508739</v>
       </c>
       <c r="V5">
-        <v>25419.510534659079</v>
+        <v>30503.412641590887</v>
       </c>
       <c r="W5">
-        <v>21686.064430742987</v>
+        <v>16264.548323057234</v>
       </c>
       <c r="X5">
-        <v>447.85000845557221</v>
+        <v>613.03646468638385</v>
       </c>
       <c r="Y5">
-        <v>289.56374774382653</v>
+        <v>163.60729764712903</v>
       </c>
       <c r="Z5">
-        <v>53686.696900541392</v>
+        <v>64424.036280649561</v>
       </c>
       <c r="AA5">
-        <v>95620.3373784447</v>
+        <v>71715.253033833549</v>
       </c>
       <c r="AB5">
-        <v>967.132849863405</v>
+        <v>1160.5594198360693</v>
       </c>
       <c r="AC5">
-        <v>830.571432486287</v>
+        <v>622.92857436471218</v>
       </c>
       <c r="AD5">
-        <v>1.0403731755062255</v>
+        <v>1.0416049389677955</v>
       </c>
       <c r="AE5">
-        <v>0.49914020720919217</v>
+        <v>0.49876661277290857</v>
       </c>
       <c r="AF5">
-        <v>430.28694046082711</v>
+        <v>591.93582476774031</v>
       </c>
       <c r="AG5">
-        <v>282.32792534288086</v>
+        <v>158.184492930943</v>
       </c>
       <c r="AH5">
-        <v>53704.259968536142</v>
+        <v>64445.1369205682</v>
       </c>
       <c r="AI5">
-        <v>95627.57320084564</v>
+        <v>71720.675838549723</v>
       </c>
       <c r="AJ5">
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>9.71716577437275E-14</v>
       </c>
       <c r="AL5">
-        <v>54134.546908996963</v>
+        <v>65037.072745335943</v>
       </c>
       <c r="AM5">
-        <v>95909.901126188517</v>
+        <v>71878.860331480682</v>
       </c>
       <c r="AN5">
-        <v>1378.0788703220767</v>
+        <v>1655.6195785403675</v>
       </c>
       <c r="AO5">
-        <v>2007.1975569571061</v>
+        <v>1504.2771513692476</v>
       </c>
       <c r="AP5">
         <v>24.935723435366441</v>
@@ -2553,124 +2553,124 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D3">
-        <v>43.078248407950049</v>
+        <v>43.325038110804336</v>
       </c>
       <c r="E3">
-        <v>42.369220466530194</v>
+        <v>42.4304828885184</v>
       </c>
       <c r="F3">
-        <v>80.946335120576222</v>
+        <v>80.865831663115571</v>
       </c>
       <c r="G3">
-        <v>80.771638929524315</v>
+        <v>80.74874271909151</v>
       </c>
       <c r="H3">
-        <v>91.467560427874034</v>
+        <v>117.60114912155233</v>
       </c>
       <c r="I3">
-        <v>143.00704677873924</v>
+        <v>95.338031185826168</v>
       </c>
       <c r="J3">
-        <v>126.35261718834684</v>
+        <v>162.45336495644591</v>
       </c>
       <c r="K3">
-        <v>109.75026529449278</v>
+        <v>73.166843529661847</v>
       </c>
       <c r="L3">
-        <v>1746.0686011935604</v>
+        <v>2244.9453443917196</v>
       </c>
       <c r="M3">
-        <v>5214.1702647945895</v>
+        <v>3476.1135098630593</v>
       </c>
       <c r="N3">
-        <v>19.08948476405914</v>
+        <v>19.089484764059137</v>
       </c>
       <c r="O3">
-        <v>36.460932396303264</v>
+        <v>36.460932396303257</v>
       </c>
       <c r="P3">
         <v>1.3813926663976253</v>
       </c>
       <c r="Q3">
-        <v>0.76744655432468711</v>
+        <v>0.767446554324687</v>
       </c>
       <c r="R3">
-        <v>240.54615015429252</v>
+        <v>350.15264151286203</v>
       </c>
       <c r="S3">
-        <v>143.6549271413387</v>
+        <v>76.867797522474476</v>
       </c>
       <c r="T3">
-        <v>42644.825159053224</v>
+        <v>54829.0609187827</v>
       </c>
       <c r="U3">
-        <v>243224.91593453163</v>
+        <v>162149.94395635443</v>
       </c>
       <c r="V3">
-        <v>2507.9838382333874</v>
+        <v>3224.5506491572105</v>
       </c>
       <c r="W3">
-        <v>4161.249136627941</v>
+        <v>2774.1660910852943</v>
       </c>
       <c r="X3">
-        <v>66.003571390163685</v>
+        <v>125.74075453041073</v>
       </c>
       <c r="Y3">
-        <v>59.4274642048599</v>
+        <v>20.716155564821971</v>
       </c>
       <c r="Z3">
-        <v>9313.2751995666968</v>
+        <v>11974.210970871473</v>
       </c>
       <c r="AA3">
-        <v>53111.406407041417</v>
+        <v>35407.604271360949</v>
       </c>
       <c r="AB3">
-        <v>95.977477517443234</v>
+        <v>123.39961395099765</v>
       </c>
       <c r="AC3">
-        <v>159.65213324909198</v>
+        <v>106.43475549939542</v>
       </c>
       <c r="AD3">
-        <v>0.59458778435515369</v>
+        <v>0.59663861029328635</v>
       </c>
       <c r="AE3">
-        <v>0.17242114537246006</v>
+        <v>0.17232904763350362</v>
       </c>
       <c r="AF3">
-        <v>65.007527966928961</v>
+        <v>124.45570987017457</v>
       </c>
       <c r="AG3">
-        <v>58.9470189258858</v>
+        <v>20.3960297978814</v>
       </c>
       <c r="AH3">
-        <v>9314.2712429899311</v>
+        <v>11975.496015531709</v>
       </c>
       <c r="AI3">
-        <v>53111.8868523204</v>
+        <v>35407.924397127885</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>2.1629257694631435E-14</v>
       </c>
       <c r="AK3">
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>9379.27877095686</v>
+        <v>12099.951725401883</v>
       </c>
       <c r="AM3">
-        <v>53170.833871246272</v>
+        <v>35428.320426925769</v>
       </c>
       <c r="AN3">
-        <v>403.93534011285863</v>
+        <v>521.105965064599</v>
       </c>
       <c r="AO3">
-        <v>1200.845087427768</v>
+        <v>800.13649294105869</v>
       </c>
       <c r="AP3">
         <v>14.793838572448902</v>
@@ -2690,124 +2690,124 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>90</v>
+        <v>812</v>
       </c>
       <c r="C4">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="D4">
-        <v>55.903109665134458</v>
+        <v>56.315053338411836</v>
       </c>
       <c r="E4">
-        <v>54.162119775631176</v>
+        <v>54.11538753627412</v>
       </c>
       <c r="F4">
-        <v>86.615910871039986</v>
+        <v>86.508722318729539</v>
       </c>
       <c r="G4">
-        <v>86.299212578084322</v>
+        <v>86.296543786970844</v>
       </c>
       <c r="H4">
-        <v>147.83001946415376</v>
+        <v>190.06716788248338</v>
       </c>
       <c r="I4">
-        <v>163.2443505702883</v>
+        <v>108.82956704685887</v>
       </c>
       <c r="J4">
-        <v>511.49950073782645</v>
+        <v>657.68465755550051</v>
       </c>
       <c r="K4">
-        <v>227.15739588741394</v>
+        <v>151.43826392494265</v>
       </c>
       <c r="L4">
-        <v>3587.6049109771834</v>
+        <v>4612.6348855420911</v>
       </c>
       <c r="M4">
-        <v>6359.2557610133372</v>
+        <v>4239.5038406755584</v>
       </c>
       <c r="N4">
-        <v>24.268446449383816</v>
+        <v>24.268446449383809</v>
       </c>
       <c r="O4">
         <v>38.955441574532315</v>
       </c>
       <c r="P4">
-        <v>3.4600516362771381</v>
+        <v>3.4602749379742446</v>
       </c>
       <c r="Q4">
         <v>1.3915176549378141</v>
       </c>
       <c r="R4">
-        <v>2069.4089817665663</v>
+        <v>2767.4490926720832</v>
       </c>
       <c r="S4">
-        <v>414.06805390260536</v>
+        <v>251.43015126236506</v>
       </c>
       <c r="T4">
-        <v>111392.87534619434</v>
+        <v>143219.41115939268</v>
       </c>
       <c r="U4">
-        <v>316934.49238931114</v>
+        <v>211289.66159287409</v>
       </c>
       <c r="V4">
-        <v>12903.146579510725</v>
+        <v>16589.759887942357</v>
       </c>
       <c r="W4">
-        <v>9201.9042763675461</v>
+        <v>6134.6028509116968</v>
       </c>
       <c r="X4">
-        <v>299.59429728371066</v>
+        <v>491.67935504261163</v>
       </c>
       <c r="Y4">
-        <v>97.97452707557045</v>
+        <v>40.70113337767512</v>
       </c>
       <c r="Z4">
-        <v>24327.277682598167</v>
+        <v>31277.928449054827</v>
       </c>
       <c r="AA4">
-        <v>69206.876133648</v>
+        <v>46137.91742243198</v>
       </c>
       <c r="AB4">
-        <v>489.84833696822523</v>
+        <v>628.77499547536263</v>
       </c>
       <c r="AC4">
-        <v>352.88761265248121</v>
+        <v>235.2584084349877</v>
       </c>
       <c r="AD4">
-        <v>1.1674327507274593</v>
+        <v>1.1695525618683607</v>
       </c>
       <c r="AE4">
-        <v>0.2925566389668916</v>
+        <v>0.29240042898802476</v>
       </c>
       <c r="AF4">
-        <v>289.61198883964073</v>
+        <v>478.84267547875788</v>
       </c>
       <c r="AG4">
-        <v>96.1726402350547</v>
+        <v>39.500516904168272</v>
       </c>
       <c r="AH4">
-        <v>24337.259991042236</v>
+        <v>31290.765128618685</v>
       </c>
       <c r="AI4">
-        <v>69208.678020488514</v>
+        <v>46139.118038905479</v>
       </c>
       <c r="AJ4">
-        <v>5.6497950155091811E-14</v>
+        <v>-1.1299590031018362E-13</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>4.6886447420039893E-14</v>
       </c>
       <c r="AL4">
-        <v>24626.871979881878</v>
+        <v>31769.607804097446</v>
       </c>
       <c r="AM4">
-        <v>69304.850660723561</v>
+        <v>46178.618555809648</v>
       </c>
       <c r="AN4">
-        <v>830.04240621893234</v>
+        <v>1070.7855460308531</v>
       </c>
       <c r="AO4">
-        <v>1464.5836296447237</v>
+        <v>975.86890573556263</v>
       </c>
       <c r="AP4">
         <v>18.807394940918407</v>
@@ -2827,40 +2827,40 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="C5">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="D5">
-        <v>79.9541980142838</v>
+        <v>80.523928876626911</v>
       </c>
       <c r="E5">
-        <v>77.654553357488453</v>
+        <v>77.607403615042557</v>
       </c>
       <c r="F5">
-        <v>97.6854659584332</v>
+        <v>97.573749451716068</v>
       </c>
       <c r="G5">
-        <v>97.384980362779189</v>
+        <v>97.372409339114554</v>
       </c>
       <c r="H5">
-        <v>304.71985697312419</v>
+        <v>391.78267325115968</v>
       </c>
       <c r="I5">
-        <v>207.90056424220626</v>
+        <v>138.60037616147085</v>
       </c>
       <c r="J5">
-        <v>1392.6998731424842</v>
+        <v>1790.7298660394886</v>
       </c>
       <c r="K5">
-        <v>274.41129373255876</v>
+        <v>182.94086248837255</v>
       </c>
       <c r="L5">
-        <v>10617.243858671272</v>
+        <v>13650.742104005918</v>
       </c>
       <c r="M5">
-        <v>9139.7128924086464</v>
+        <v>6093.1419282724319</v>
       </c>
       <c r="N5">
         <v>34.842638625968164</v>
@@ -2869,82 +2869,82 @@
         <v>43.961943661493812</v>
       </c>
       <c r="P5">
-        <v>4.5704270373995275</v>
+        <v>4.57072246503231</v>
       </c>
       <c r="Q5">
         <v>1.3199160605108644</v>
       </c>
       <c r="R5">
-        <v>7528.03951071305</v>
+        <v>10132.606913348956</v>
       </c>
       <c r="S5">
-        <v>506.12235663702472</v>
+        <v>297.49047653279052</v>
       </c>
       <c r="T5">
-        <v>473296.89770663291</v>
+        <v>608524.58276567073</v>
       </c>
       <c r="U5">
-        <v>514049.00353702274</v>
+        <v>342699.33569134853</v>
       </c>
       <c r="V5">
-        <v>50443.522419956025</v>
+        <v>64855.957397086306</v>
       </c>
       <c r="W5">
-        <v>12544.83673273782</v>
+        <v>8363.22448849188</v>
       </c>
       <c r="X5">
-        <v>1162.8063555197496</v>
+        <v>1947.6776858379649</v>
       </c>
       <c r="Y5">
-        <v>143.92248285385622</v>
+        <v>56.02389401067807</v>
       </c>
       <c r="Z5">
-        <v>103364.10673517006</v>
+        <v>132896.70865950434</v>
       </c>
       <c r="AA5">
-        <v>112249.46027872519</v>
+        <v>74832.973519150109</v>
       </c>
       <c r="AB5">
-        <v>1918.184025620759</v>
+        <v>2462.2037979440338</v>
       </c>
       <c r="AC5">
-        <v>481.18289758944525</v>
+        <v>320.78859839296223</v>
       </c>
       <c r="AD5">
-        <v>1.0748617877481994</v>
+        <v>1.0768116430620662</v>
       </c>
       <c r="AE5">
-        <v>0.24592069709707615</v>
+        <v>0.24578940314556474</v>
       </c>
       <c r="AF5">
-        <v>1126.817236733468</v>
+        <v>1901.3978037337504</v>
       </c>
       <c r="AG5">
-        <v>141.85717261157575</v>
+        <v>54.6477556201993</v>
       </c>
       <c r="AH5">
-        <v>103400.09585395634</v>
+        <v>132942.98854160856</v>
       </c>
       <c r="AI5">
-        <v>112251.52558896747</v>
+        <v>74834.349657540588</v>
       </c>
       <c r="AJ5">
-        <v>-2.40053993148876E-13</v>
+        <v>-4.80107986297752E-13</v>
       </c>
       <c r="AK5">
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>104526.91309068982</v>
+        <v>134844.3863453423</v>
       </c>
       <c r="AM5">
-        <v>112393.38276157904</v>
+        <v>74888.997413160774</v>
       </c>
       <c r="AN5">
-        <v>2456.4277071614119</v>
+        <v>3168.8990899315422</v>
       </c>
       <c r="AO5">
-        <v>2104.9299866067313</v>
+        <v>1402.5389435628135</v>
       </c>
       <c r="AP5">
         <v>27.002110200544795</v>
